--- a/data/Normal Day.xlsx
+++ b/data/Normal Day.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4th year\sem 2\EEX5362 Perfomance Modeling\Miniproject\github\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Normal day" sheetId="1" r:id="rId4"/>
+    <sheet name="Normal day" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="9">
   <si>
     <t>customerId</t>
   </si>
@@ -43,55 +51,80 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -281,17 +314,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:G57"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -311,49 +352,49 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1">
         <v>2.5</v>
       </c>
       <c r="C2" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E2" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D3" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E3" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1">
         <v>7.8</v>
@@ -365,84 +406,84 @@
         <v>3.5</v>
       </c>
       <c r="E4" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1">
         <v>16.5</v>
       </c>
       <c r="C7" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1">
         <v>2.5</v>
       </c>
       <c r="D8" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1">
         <v>7.5</v>
@@ -451,49 +492,49 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1">
         <v>19.2</v>
       </c>
       <c r="C9" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D9" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E9" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D10" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1">
         <v>25.5</v>
@@ -505,44 +546,44 @@
         <v>4.5</v>
       </c>
       <c r="E11" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="C12" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E12" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1">
         <v>1.2</v>
       </c>
       <c r="D13" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E13" s="1">
         <v>6.2</v>
@@ -551,15 +592,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="1">
         <v>6.5</v>
@@ -571,9 +612,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1">
         <v>33.5</v>
@@ -582,7 +623,7 @@
         <v>4.5</v>
       </c>
       <c r="D15" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E15" s="1">
         <v>7.5</v>
@@ -591,38 +632,38 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>36.0</v>
+        <v>36</v>
       </c>
       <c r="C16" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D16" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E16" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1">
         <v>0.2</v>
       </c>
       <c r="D17" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E17" s="1">
         <v>4.2</v>
@@ -631,15 +672,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1">
         <v>42.1</v>
       </c>
       <c r="C18" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D18" s="1">
         <v>5.5</v>
@@ -651,95 +692,95 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>45.0</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E19" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>48.0</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D20" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E20" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D21" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E21" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1">
         <v>52.5</v>
       </c>
       <c r="C22" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E22" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D23" s="1">
         <v>3.5</v>
@@ -751,27 +792,588 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="B24" s="1">
-        <v>58.0</v>
-      </c>
-      <c r="C24" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="D24" s="1" t="s">
+    <row r="24" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3">
+        <v>58</v>
+      </c>
+      <c r="C24" s="3">
+        <v>5</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>65.3</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25">
+        <v>4</v>
+      </c>
+      <c r="F25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>67.3</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>70.3</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+      <c r="F27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>73.400000000000006</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>75</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>78.5</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>6</v>
+      </c>
+      <c r="E31">
+        <v>6</v>
+      </c>
+      <c r="F31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>83.6</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32">
+        <v>3</v>
+      </c>
+      <c r="F32" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>86.7</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="F33" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>90.6</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34">
+        <v>4</v>
+      </c>
+      <c r="F34" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>93.4</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <v>4</v>
+      </c>
+      <c r="F35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>95.4</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>6</v>
+      </c>
+      <c r="E36">
+        <v>6</v>
+      </c>
+      <c r="F36" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>98.7</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>7</v>
+      </c>
+      <c r="E37">
+        <v>7</v>
+      </c>
+      <c r="F37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>101.3</v>
+      </c>
+      <c r="C38">
+        <v>0.1</v>
+      </c>
+      <c r="D38">
+        <v>3</v>
+      </c>
+      <c r="E38">
+        <v>3.1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>104.4</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>6</v>
+      </c>
+      <c r="E39">
+        <v>6</v>
+      </c>
+      <c r="F39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>107</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>6</v>
+      </c>
+      <c r="E40">
+        <v>6</v>
+      </c>
+      <c r="F40" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>109.9</v>
+      </c>
+      <c r="C41">
+        <v>0.5</v>
+      </c>
+      <c r="D41">
+        <v>5</v>
+      </c>
+      <c r="E41">
+        <v>5.5</v>
+      </c>
+      <c r="F41" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>112.9</v>
+      </c>
+      <c r="C42">
+        <v>0.1</v>
+      </c>
+      <c r="D42">
+        <v>6</v>
+      </c>
+      <c r="E42">
+        <v>6.1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>116.1</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>5</v>
+      </c>
+      <c r="E43">
+        <v>5</v>
+      </c>
+      <c r="F43" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>119.2</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>4</v>
+      </c>
+      <c r="E44">
+        <v>4</v>
+      </c>
+      <c r="F44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>122.5</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>7</v>
+      </c>
+      <c r="E45">
+        <v>7</v>
+      </c>
+      <c r="F45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>124.9</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>6</v>
+      </c>
+      <c r="E46">
+        <v>6</v>
+      </c>
+      <c r="F46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>127.8</v>
+      </c>
+      <c r="C47">
+        <v>1.7</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47">
+        <v>5.7</v>
+      </c>
+      <c r="F47" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>130.80000000000001</v>
+      </c>
+      <c r="C48">
+        <v>0.1</v>
+      </c>
+      <c r="D48">
+        <v>6</v>
+      </c>
+      <c r="E48">
+        <v>6.1</v>
+      </c>
+      <c r="F48" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>132.5</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49">
+        <v>4</v>
+      </c>
+      <c r="F49" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>134.6</v>
+      </c>
+      <c r="C50">
+        <v>1.9</v>
+      </c>
+      <c r="D50">
+        <v>6</v>
+      </c>
+      <c r="E50">
+        <v>7.9</v>
+      </c>
+      <c r="F50" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4">
+        <v>138</v>
+      </c>
+      <c r="C51" s="4">
+        <v>0</v>
+      </c>
+      <c r="D51" s="4">
+        <v>3</v>
+      </c>
+      <c r="E51" s="4">
+        <v>3</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="4"/>
+    </row>
+    <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2"/>
+    </row>
+    <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2"/>
+    </row>
+    <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2"/>
+    </row>
+    <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2"/>
+    </row>
+    <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2"/>
+    </row>
+    <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>